--- a/hardware/expansion-board-v4/CHECKLIST-V4.6.xlsx
+++ b/hardware/expansion-board-v4/CHECKLIST-V4.6.xlsx
@@ -6425,7 +6425,7 @@
       </c>
       <c r="G208" s="13" t="inlineStr">
         <is>
-          <t>有源器件(TCXO/OSC)，四脚功能各异（VDD/GND/OUT/NC），认 pin1 标记；转 180° 会把 VDD 接到 GND 上，上电即烧</t>
+          <t>有源 TCXO：pin2=GND / pin4=Vcc，转 180° 直接短路、上电即烧。顶面无标记，倒角在底面 #1 角（手册 C0.2）——贴前翻过来认，或先用一颗定出「底面倒角↔顶面打标」的对应关系再批量贴；板上丝印的实心圆点指向 pin1</t>
         </is>
       </c>
     </row>
